--- a/output/risultati.xlsx
+++ b/output/risultati.xlsx
@@ -5,28 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gi.gaglione\Desktop\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gi.gaglione\Documents\GitHub\idd-hw6-record-linkage\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98639B1D-18F4-4465-B69F-7517E75BD3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BF5667-668C-4962-B8BF-D4D1C1D0CA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$18:$C$33</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$G$17</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$G$18:$G$33</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$H$17</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$H$18:$H$33</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$18:$C$33</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$G$17</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$G$18:$G$33</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$H$17</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$H$18:$H$33</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="32">
   <si>
     <t>Pipeline</t>
   </si>
@@ -125,6 +113,18 @@
   <si>
     <t>/</t>
   </si>
+  <si>
+    <t>Record Linkage</t>
+  </si>
+  <si>
+    <t>Ditto</t>
+  </si>
+  <si>
+    <t>//</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
 </sst>
 </file>
 
@@ -133,16 +133,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -164,7 +156,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -187,11 +179,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -232,18 +280,53 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -435,6 +518,9 @@
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.59950000000000003</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -597,6 +683,9 @@
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.84640000000000004</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -758,6 +847,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.70179999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1102,7 +1194,7 @@
             <c:numRef>
               <c:f>Sheet1!$G$18:$G$33</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>150.31</c:v>
@@ -1276,7 +1368,7 @@
             <c:numRef>
               <c:f>Sheet1!$H$18:$H$33</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>3.74</c:v>
@@ -1421,7 +1513,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1641,17 +1733,26 @@
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.36330000000000001</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0.81269999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.7238</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.52800000000000002</c:v>
+                </c:pt>
                 <c:pt idx="4">
                   <c:v>0.83840000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.91669999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.48880000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.89959999999999996</c:v>
@@ -1755,17 +1856,26 @@
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.96409999999999996</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0.43940000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.13739999999999999</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.9869</c:v>
+                </c:pt>
                 <c:pt idx="4">
                   <c:v>0.15010000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>7.9600000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.99670000000000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.40510000000000002</c:v>
@@ -1869,17 +1979,26 @@
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.52769999999999995</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>0.57040000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.23100000000000001</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.68789999999999996</c:v>
+                </c:pt>
                 <c:pt idx="4">
                   <c:v>0.25459999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.1464</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.65590000000000004</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.55859999999999999</c:v>
@@ -2209,19 +2328,28 @@
             <c:numRef>
               <c:f>Sheet1!$G$3:$G$11</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>119.27760000000001</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>194.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>322.16000000000003</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>124.2073</c:v>
+                </c:pt>
                 <c:pt idx="4">
                   <c:v>188.89</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>245.75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0397000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.14000000000000001</c:v>
@@ -2329,19 +2457,28 @@
             <c:numRef>
               <c:f>Sheet1!$H$3:$H$11</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>455.9427</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>6.43</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>8.0399999999999991</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>515.38509999999997</c:v>
+                </c:pt>
                 <c:pt idx="4">
                   <c:v>7.03</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>7.87</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.28029999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.02</c:v>
@@ -2444,7 +2581,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3259,7 +3396,7 @@
             <c:numRef>
               <c:f>Sheet1!$G$40:$G$48</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>403.49189200000001</c:v>
@@ -3388,7 +3525,7 @@
             <c:numRef>
               <c:f>Sheet1!$H$40:$H$48</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.689079</c:v>
@@ -3512,6 +3649,569 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="122272128"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="it-IT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="it-IT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AO$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Record Linkage</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$AM$4:$AN$12</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="9"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Baseline</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>B1</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>B2</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Baseline</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>B1</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>B2</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Baseline</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>B1</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>B2</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>P1</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>P2</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>P3</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AO$4:$AO$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.52769999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.57040000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.23100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.68789999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25459999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.1464</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.65590000000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.55859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.32079999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9061-41CC-B213-23508D37A2F0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AP$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dedupe</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$AM$4:$AN$12</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="9"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Baseline</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>B1</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>B2</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Baseline</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>B1</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>B2</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Baseline</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>B1</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>B2</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>P1</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>P2</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>P3</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AP$4:$AP$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.78369999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.6875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4325</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.82489999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.70030000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.50590000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.91969999999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.77500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.5615</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9061-41CC-B213-23508D37A2F0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AQ$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ditto</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$AM$4:$AN$12</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="9"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Baseline</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>B1</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>B2</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Baseline</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>B1</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>B2</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Baseline</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>B1</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>B2</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>P1</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>P2</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>P3</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AQ$4:$AQ$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.99180000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.88319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.88590000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99670000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.86870000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.87539999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.995</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.91479999999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.92410000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9061-41CC-B213-23508D37A2F0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="269184544"/>
+        <c:axId val="269185376"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="269184544"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="269185376"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="269185376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3543,7 +4243,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="122272128"/>
+        <c:crossAx val="269184544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3867,6 +4567,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -6397,6 +7137,509 @@
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6903,15 +8146,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>41661</xdr:rowOff>
+      <xdr:rowOff>143681</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>72828</xdr:rowOff>
+      <xdr:rowOff>178658</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6939,15 +8182,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>75700</xdr:colOff>
+      <xdr:colOff>1618</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>66269</xdr:rowOff>
+      <xdr:rowOff>168289</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>588738</xdr:colOff>
+      <xdr:colOff>524181</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>70079</xdr:rowOff>
+      <xdr:rowOff>174004</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7011,15 +8254,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>181130</xdr:colOff>
+      <xdr:colOff>60904</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>58711</xdr:rowOff>
+      <xdr:rowOff>142528</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>549639</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>162393</xdr:rowOff>
+      <xdr:colOff>440843</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66294</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7047,15 +8290,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>31228</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>46220</xdr:rowOff>
+      <xdr:colOff>37154</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>172164</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>599606</xdr:colOff>
+      <xdr:colOff>575156</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>149902</xdr:rowOff>
+      <xdr:rowOff>169505</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7083,15 +8326,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>143655</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>21235</xdr:rowOff>
+      <xdr:colOff>16558</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>175099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>237344</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>24982</xdr:rowOff>
+      <xdr:colOff>98817</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>173131</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7111,6 +8354,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>250191</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9104</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>325120</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>103930</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Grafico 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDB8410F-16F3-416D-8F04-6361B41A7CA7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7382,7 +8661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:O49"/>
+  <dimension ref="A2:AQ49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -7390,11 +8669,14 @@
     <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" style="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.5546875" customWidth="1"/>
+    <col min="40" max="40" width="10" customWidth="1"/>
+    <col min="41" max="41" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>10</v>
       </c>
@@ -7404,19 +8686,19 @@
       <c r="C2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="30" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="14" t="s">
@@ -7430,27 +8712,61 @@
       </c>
       <c r="L2" s="15"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="28" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
+      <c r="D3" s="9">
+        <v>0.36330000000000001</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.96409999999999996</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.52769999999999995</v>
+      </c>
+      <c r="G3" s="31">
+        <v>119.27760000000001</v>
+      </c>
+      <c r="H3" s="31">
+        <v>455.9427</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>27</v>
+      </c>
       <c r="L3" s="16"/>
+      <c r="AL3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO3" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="AP3" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ3" s="24" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:43" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13"/>
-      <c r="B4" s="18"/>
+      <c r="B4" s="28"/>
       <c r="C4" s="12" t="s">
         <v>19</v>
       </c>
@@ -7463,10 +8779,10 @@
       <c r="F4" s="9">
         <v>0.57040000000000002</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="31">
         <v>194.1</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="31">
         <v>6.43</v>
       </c>
       <c r="I4" s="10">
@@ -7479,10 +8795,25 @@
         <v>297</v>
       </c>
       <c r="L4" s="16"/>
+      <c r="AM4" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN4" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO4" s="9">
+        <v>0.52769999999999995</v>
+      </c>
+      <c r="AP4" s="23">
+        <v>0.78369999999999995</v>
+      </c>
+      <c r="AQ4" s="23">
+        <v>0.99180000000000001</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" s="13"/>
-      <c r="B5" s="18"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="12" t="s">
         <v>20</v>
       </c>
@@ -7495,10 +8826,10 @@
       <c r="F5" s="9">
         <v>0.23100000000000001</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="31">
         <v>322.16000000000003</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="31">
         <v>8.0399999999999991</v>
       </c>
       <c r="I5" s="10">
@@ -7511,28 +8842,70 @@
         <v>103</v>
       </c>
       <c r="L5" s="16"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO5" s="9">
+        <v>0.57040000000000002</v>
+      </c>
+      <c r="AP5" s="9">
+        <v>0.6875</v>
+      </c>
+      <c r="AQ5" s="9">
+        <v>0.88319999999999999</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13"/>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="28" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+      <c r="D6" s="9">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.9869</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0.68789999999999996</v>
+      </c>
+      <c r="G6" s="31">
+        <v>124.2073</v>
+      </c>
+      <c r="H6" s="31">
+        <v>515.38509999999997</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>27</v>
+      </c>
       <c r="L6" s="16"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO6" s="26">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="AP6" s="26">
+        <v>0.4325</v>
+      </c>
+      <c r="AQ6" s="26">
+        <v>0.88590000000000002</v>
+      </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:43" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13"/>
-      <c r="B7" s="18"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="12" t="s">
         <v>19</v>
       </c>
@@ -7545,10 +8918,10 @@
       <c r="F7" s="9">
         <v>0.25459999999999999</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="31">
         <v>188.89</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="31">
         <v>7.03</v>
       </c>
       <c r="I7" s="10">
@@ -7561,10 +8934,25 @@
         <v>97</v>
       </c>
       <c r="L7" s="16"/>
+      <c r="AM7" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN7" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO7" s="23">
+        <v>0.68789999999999996</v>
+      </c>
+      <c r="AP7" s="23">
+        <v>0.82489999999999997</v>
+      </c>
+      <c r="AQ7" s="23">
+        <v>0.99670000000000003</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
-      <c r="B8" s="18"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="12" t="s">
         <v>20</v>
       </c>
@@ -7577,10 +8965,10 @@
       <c r="F8" s="9">
         <v>0.1464</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="31">
         <v>245.75</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="31">
         <v>7.87</v>
       </c>
       <c r="I8" s="10">
@@ -7593,28 +8981,70 @@
         <v>45</v>
       </c>
       <c r="L8" s="16"/>
+      <c r="AM8" s="28"/>
+      <c r="AN8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO8" s="9">
+        <v>0.25459999999999999</v>
+      </c>
+      <c r="AP8" s="9">
+        <v>0.70030000000000003</v>
+      </c>
+      <c r="AQ8" s="9">
+        <v>0.86870000000000003</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="D9" s="9">
+        <v>0.48880000000000001</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.99670000000000003</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.65590000000000004</v>
+      </c>
+      <c r="G9" s="31">
+        <v>1.0397000000000001</v>
+      </c>
+      <c r="H9" s="31">
+        <v>0.28029999999999999</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>27</v>
+      </c>
       <c r="L9" s="16"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO9" s="26">
+        <v>0.1464</v>
+      </c>
+      <c r="AP9" s="26">
+        <v>0.50590000000000002</v>
+      </c>
+      <c r="AQ9" s="26">
+        <v>0.87539999999999996</v>
+      </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:43" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
-      <c r="B10" s="18"/>
+      <c r="B10" s="28"/>
       <c r="C10" s="12" t="s">
         <v>19</v>
       </c>
@@ -7627,10 +9057,10 @@
       <c r="F10" s="9">
         <v>0.55859999999999999</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="31">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="31">
         <v>0.02</v>
       </c>
       <c r="I10" s="10">
@@ -7643,10 +9073,25 @@
         <v>247</v>
       </c>
       <c r="L10" s="16"/>
+      <c r="AM10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN10" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO10" s="23">
+        <v>0.65590000000000004</v>
+      </c>
+      <c r="AP10" s="23">
+        <v>0.91969999999999996</v>
+      </c>
+      <c r="AQ10" s="23">
+        <v>0.995</v>
+      </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
-      <c r="B11" s="18"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="12" t="s">
         <v>20</v>
       </c>
@@ -7659,10 +9104,10 @@
       <c r="F11" s="9">
         <v>0.32079999999999997</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="31">
         <v>0.15</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="31">
         <v>0.01</v>
       </c>
       <c r="I11" s="10">
@@ -7675,51 +9120,77 @@
         <v>111</v>
       </c>
       <c r="L11" s="16"/>
+      <c r="AM11" s="28"/>
+      <c r="AN11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO11" s="9">
+        <v>0.55859999999999999</v>
+      </c>
+      <c r="AP11" s="9">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="AQ11" s="9">
+        <v>0.91479999999999995</v>
+      </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="17" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="18">
         <v>0.78990000000000005</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="18">
         <v>0.42009999999999997</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="18">
         <v>0.54849999999999999</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="K12" s="18" t="s">
         <v>27</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO12" s="26">
+        <v>0.32079999999999997</v>
+      </c>
+      <c r="AP12" s="26">
+        <v>0.5615</v>
+      </c>
+      <c r="AQ12" s="26">
+        <v>0.92410000000000003</v>
+      </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:43" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B13" s="7"/>
       <c r="C13" s="8"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="6"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -7727,15 +9198,30 @@
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
+      <c r="AM13" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN13" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO13" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP13" s="23">
+        <v>0.91969999999999996</v>
+      </c>
+      <c r="AQ13" s="23" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
@@ -7743,9 +9229,35 @@
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
+      <c r="AM14" s="28"/>
+      <c r="AN14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP14" s="9">
+        <v>0.71840000000000004</v>
+      </c>
+      <c r="AQ14" s="9" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
+      <c r="AM15" s="28"/>
+      <c r="AN15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="9" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
@@ -7757,19 +9269,19 @@
       <c r="C17" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="30" t="s">
         <v>5</v>
       </c>
       <c r="I17" s="14" t="s">
@@ -7784,7 +9296,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="28" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -7799,10 +9311,10 @@
       <c r="F18" s="9">
         <v>0.78369999999999995</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="31">
         <v>150.31</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="31">
         <v>3.74</v>
       </c>
       <c r="I18" s="10">
@@ -7817,7 +9329,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
-      <c r="B19" s="18"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="12" t="s">
         <v>19</v>
       </c>
@@ -7830,10 +9342,10 @@
       <c r="F19" s="9">
         <v>0.6875</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="31">
         <v>157.19999999999999</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="31">
         <v>1.22</v>
       </c>
       <c r="I19" s="10">
@@ -7848,7 +9360,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
-      <c r="B20" s="18"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="12" t="s">
         <v>20</v>
       </c>
@@ -7861,10 +9373,10 @@
       <c r="F20" s="9">
         <v>0.4325</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="31">
         <v>91.28</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="31">
         <v>1.24</v>
       </c>
       <c r="I20" s="10">
@@ -7879,7 +9391,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
-      <c r="B21" s="18"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="12" t="s">
         <v>21</v>
       </c>
@@ -7892,10 +9404,10 @@
       <c r="F21" s="9">
         <v>0.51639999999999997</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="31">
         <v>166</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="31">
         <v>1.22</v>
       </c>
       <c r="I21" s="10">
@@ -7910,7 +9422,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="28" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="12" t="s">
@@ -7925,10 +9437,10 @@
       <c r="F22" s="9">
         <v>0.82489999999999997</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="31">
         <v>142.18</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="31">
         <v>9.59</v>
       </c>
       <c r="I22" s="10">
@@ -7943,7 +9455,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
-      <c r="B23" s="18"/>
+      <c r="B23" s="28"/>
       <c r="C23" s="12" t="s">
         <v>19</v>
       </c>
@@ -7956,10 +9468,10 @@
       <c r="F23" s="9">
         <v>0.70030000000000003</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="31">
         <v>134.58000000000001</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="31">
         <v>0.82</v>
       </c>
       <c r="I23" s="10">
@@ -7974,7 +9486,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
-      <c r="B24" s="18"/>
+      <c r="B24" s="28"/>
       <c r="C24" s="12" t="s">
         <v>20</v>
       </c>
@@ -7987,10 +9499,10 @@
       <c r="F24" s="9">
         <v>0.50590000000000002</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="31">
         <v>128.52000000000001</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="31">
         <v>3.02</v>
       </c>
       <c r="I24" s="10">
@@ -8005,7 +9517,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
-      <c r="B25" s="18"/>
+      <c r="B25" s="28"/>
       <c r="C25" s="12" t="s">
         <v>21</v>
       </c>
@@ -8018,10 +9530,10 @@
       <c r="F25" s="9">
         <v>0.52769999999999995</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="31">
         <v>133.29</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="31">
         <v>3.09</v>
       </c>
       <c r="I25" s="10">
@@ -8036,7 +9548,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
@@ -8051,10 +9563,10 @@
       <c r="F26" s="9">
         <v>0.91969999999999996</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="31">
         <v>55.89</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="31">
         <v>0.59</v>
       </c>
       <c r="I26" s="10">
@@ -8069,7 +9581,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
-      <c r="B27" s="18"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="12" t="s">
         <v>19</v>
       </c>
@@ -8082,10 +9594,10 @@
       <c r="F27" s="9">
         <v>0.77500000000000002</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="31">
         <v>53.74</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="31">
         <v>0.57999999999999996</v>
       </c>
       <c r="I27" s="10">
@@ -8100,7 +9612,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
-      <c r="B28" s="18"/>
+      <c r="B28" s="28"/>
       <c r="C28" s="12" t="s">
         <v>20</v>
       </c>
@@ -8113,10 +9625,10 @@
       <c r="F28" s="9">
         <v>0.5615</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="31">
         <v>55.38</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="31">
         <v>0.78</v>
       </c>
       <c r="I28" s="10">
@@ -8131,7 +9643,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
-      <c r="B29" s="18"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="12" t="s">
         <v>21</v>
       </c>
@@ -8144,10 +9656,10 @@
       <c r="F29" s="9">
         <v>0.56789999999999996</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="31">
         <v>56.07</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="31">
         <v>0.82</v>
       </c>
       <c r="I29" s="10">
@@ -8162,7 +9674,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="12" t="s">
@@ -8177,10 +9689,10 @@
       <c r="F30" s="9">
         <v>0.91969999999999996</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="31">
         <v>52.96</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="31">
         <v>0.57999999999999996</v>
       </c>
       <c r="I30" s="10">
@@ -8195,7 +9707,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
-      <c r="B31" s="18"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="12" t="s">
         <v>19</v>
       </c>
@@ -8208,10 +9720,10 @@
       <c r="F31" s="9">
         <v>0.71840000000000004</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="31">
         <v>59.48</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="31">
         <v>0.61</v>
       </c>
       <c r="I31" s="10">
@@ -8226,7 +9738,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>
-      <c r="B32" s="18"/>
+      <c r="B32" s="28"/>
       <c r="C32" s="12" t="s">
         <v>20</v>
       </c>
@@ -8239,10 +9751,10 @@
       <c r="F32" s="9">
         <v>0</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="31">
         <v>57.22</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="31">
         <v>0.71</v>
       </c>
       <c r="I32" s="10">
@@ -8257,7 +9769,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
-      <c r="B33" s="18"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="12" t="s">
         <v>21</v>
       </c>
@@ -8270,10 +9782,10 @@
       <c r="F33" s="9">
         <v>0</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="31">
         <v>57.47</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="31">
         <v>0.74</v>
       </c>
       <c r="I33" s="10">
@@ -8291,22 +9803,28 @@
         <v>24</v>
       </c>
       <c r="C34" s="4"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19" t="s">
+      <c r="D34" s="18">
+        <v>0.59950000000000003</v>
+      </c>
+      <c r="E34" s="18">
+        <v>0.84640000000000004</v>
+      </c>
+      <c r="F34" s="18">
+        <v>0.70179999999999998</v>
+      </c>
+      <c r="G34" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="H34" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="I34" s="19" t="s">
+      <c r="I34" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="J34" s="19" t="s">
+      <c r="J34" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="K34" s="19" t="s">
+      <c r="K34" s="18" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8320,24 +9838,24 @@
       <c r="C39" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H39" s="14" t="s">
+      <c r="H39" s="30" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="28" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="12" t="s">
@@ -8352,15 +9870,15 @@
       <c r="F40" s="9">
         <v>0.99180000000000001</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="31">
         <v>403.49189200000001</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="31">
         <v>0.689079</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="18"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="12" t="s">
         <v>19</v>
       </c>
@@ -8373,15 +9891,15 @@
       <c r="F41" s="9">
         <v>0.88319999999999999</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="31">
         <v>88.17</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="31">
         <v>3.0000000000000001E-6</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B42" s="18"/>
+      <c r="B42" s="28"/>
       <c r="C42" s="12" t="s">
         <v>20</v>
       </c>
@@ -8394,15 +9912,15 @@
       <c r="F42" s="9">
         <v>0.88590000000000002</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="31">
         <v>77.77</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="28" t="s">
         <v>13</v>
       </c>
       <c r="C43" s="12" t="s">
@@ -8417,15 +9935,15 @@
       <c r="F43" s="9">
         <v>0.99670000000000003</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="31">
         <v>445.57469200000003</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="31">
         <v>0.89265099999999997</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B44" s="18"/>
+      <c r="B44" s="28"/>
       <c r="C44" s="12" t="s">
         <v>19</v>
       </c>
@@ -8438,15 +9956,15 @@
       <c r="F44" s="9">
         <v>0.86870000000000003</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="31">
         <v>107.22</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="31">
         <v>5.0000000000000004E-6</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B45" s="18"/>
+      <c r="B45" s="28"/>
       <c r="C45" s="12" t="s">
         <v>20</v>
       </c>
@@ -8459,15 +9977,15 @@
       <c r="F45" s="9">
         <v>0.87539999999999996</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="31">
         <v>102.41</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="31">
         <v>3.0000000000000001E-6</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="28" t="s">
         <v>14</v>
       </c>
       <c r="C46" s="12" t="s">
@@ -8482,15 +10000,15 @@
       <c r="F46" s="9">
         <v>0.995</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="31">
         <v>345.09080999999998</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="31">
         <v>0.35250500000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B47" s="18"/>
+      <c r="B47" s="28"/>
       <c r="C47" s="12" t="s">
         <v>19</v>
       </c>
@@ -8503,15 +10021,15 @@
       <c r="F47" s="9">
         <v>0.91479999999999995</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="31">
         <v>58.28</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="31">
         <v>3.0000000000000001E-6</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="18"/>
+      <c r="B48" s="28"/>
       <c r="C48" s="12" t="s">
         <v>20</v>
       </c>
@@ -8524,10 +10042,10 @@
       <c r="F48" s="9">
         <v>0.92410000000000003</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="31">
         <v>118.81</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="31">
         <v>3.9999999999999998E-6</v>
       </c>
     </row>
@@ -8547,10 +10065,10 @@
       <c r="F49" s="9">
         <v>0.99960000000000004</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="31" t="s">
         <v>27</v>
       </c>
       <c r="I49" s="6"/>
@@ -8558,17 +10076,21 @@
       <c r="K49" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B43:B45"/>
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="B26:B29"/>
     <mergeCell ref="B30:B33"/>
+    <mergeCell ref="AM4:AM6"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AM10:AM12"/>
+    <mergeCell ref="AM13:AM15"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B43:B45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
